--- a/mine/data/Excel/Project.xlsx
+++ b/mine/data/Excel/Project.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\MineGlobe\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\MineGlobe\mine\data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3889C95C-A4EC-4392-A0F4-AEB8AB222EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0FF245-52F1-42D4-96AA-7ABE4F1E12D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3849" yWindow="1843" windowWidth="16457" windowHeight="8426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,11 +98,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/Project/Project_CardGame.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Project/Project_CookGame.html</t>
+    <t>Project/Project_CardGame.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Project/Project_CookGame.html</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
